--- a/astro-site/public/dl/kit-plan-financiero/06-dashboard-ratios-financieros.xlsx
+++ b/astro-site/public/dl/kit-plan-financiero/06-dashboard-ratios-financieros.xlsx
@@ -1,17 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView activeTab="0" autoFilterDateGrouping="1" firstSheet="0" minimized="0" showHorizontalScroll="1" showSheetTabs="1" showVerticalScroll="1" tabRatio="600" visibility="visible"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Ratios" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Benchmarks" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Instrucciones" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Ratios" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Benchmarks" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
-  <definedNames/>
+  <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Ratios'!$5:$5</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Benchmarks'!$3:$3</definedName>
+  </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
@@ -19,8 +22,8 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="2">
-    <numFmt formatCode="#,##0.00 €" numFmtId="164"/>
-    <numFmt formatCode="0.0%" numFmtId="165"/>
+    <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
+    <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
   <fonts count="12">
     <font>
@@ -154,54 +157,54 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="20">
-    <xf borderId="0" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="1" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="5" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf borderId="0" fillId="0" fontId="6" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="2" fontId="7" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="3" fontId="8" numFmtId="3" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="3" fontId="8" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf borderId="1" fillId="0" fontId="10" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="11" numFmtId="165" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="0" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="0" fontId="11" numFmtId="164" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="4" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="5" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf applyAlignment="1" borderId="1" fillId="6" fontId="8" numFmtId="0" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle builtinId="0" hidden="0" name="Normal" xfId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -561,15 +564,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="B2:B15"/>
+  <dimension ref="A1:B17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="85"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="85" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
+    <row r="1"/>
     <row r="2">
       <c r="B2" s="1" t="inlineStr">
         <is>
@@ -577,6 +581,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="2" t="inlineStr">
         <is>
@@ -584,6 +589,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="B6" s="3" t="inlineStr">
         <is>
@@ -612,9 +618,7 @@
         </is>
       </c>
     </row>
-    <row r="10">
-      <c r="B10" t="inlineStr"/>
-    </row>
+    <row r="10"/>
     <row r="11">
       <c r="B11" s="3" t="inlineStr">
         <is>
@@ -650,8 +654,25 @@
         </is>
       </c>
     </row>
+    <row r="16"/>
+    <row r="17">
+      <c r="B17" s="4" t="inlineStr">
+        <is>
+          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-plan-financiero · info@aichef.pro</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -660,16 +681,16 @@
   <sheetPr>
     <tabColor rgb="001565C0"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="35"/>
-    <col customWidth="1" max="3" min="3" width="18"/>
-    <col customWidth="1" max="4" min="4" width="20"/>
-    <col customWidth="1" max="5" min="5" width="18"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -686,6 +707,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="B4" s="6" t="inlineStr">
         <is>
@@ -809,6 +831,8 @@
       </c>
       <c r="D12" s="10" t="inlineStr"/>
     </row>
+    <row r="13"/>
+    <row r="14"/>
     <row r="15">
       <c r="B15" s="6" t="inlineStr">
         <is>
@@ -847,16 +871,16 @@
       </c>
       <c r="C17" s="13">
         <f>C7/C6</f>
-        <v/>
+        <v>0.3</v>
       </c>
       <c r="D17" s="14" t="inlineStr">
         <is>
           <t>28% - 32%</t>
         </is>
       </c>
-      <c r="E17" s="15">
+      <c r="E17" s="15" t="str">
         <f>IF(C17&lt;0.28,"✅ Excelente",IF(C17&lt;0.33,"⚠️ Aceptable","🔴 Alto"))</f>
-        <v/>
+        <v>⚠️ Aceptable</v>
       </c>
     </row>
     <row r="18">
@@ -867,16 +891,16 @@
       </c>
       <c r="C18" s="13">
         <f>C8/C6</f>
-        <v/>
+        <v>0.28</v>
       </c>
       <c r="D18" s="14" t="inlineStr">
         <is>
           <t>25% - 30%</t>
         </is>
       </c>
-      <c r="E18" s="15">
+      <c r="E18" s="15" t="str">
         <f>IF(C18&lt;0.25,"✅ Excelente",IF(C18&lt;0.31,"⚠️ Aceptable","🔴 Alto"))</f>
-        <v/>
+        <v>⚠️ Aceptable</v>
       </c>
     </row>
     <row r="19">
@@ -887,16 +911,16 @@
       </c>
       <c r="C19" s="13">
         <f>(C7+C8)/C6</f>
-        <v/>
+        <v>0.58</v>
       </c>
       <c r="D19" s="14" t="inlineStr">
         <is>
           <t>&lt; 65%</t>
         </is>
       </c>
-      <c r="E19" s="15">
+      <c r="E19" s="15" t="str">
         <f>IF(C19&lt;0.6,"✅ Excelente",IF(C19&lt;0.66,"⚠️ Aceptable","🔴 Alto"))</f>
-        <v/>
+        <v>✅ Excelente</v>
       </c>
     </row>
     <row r="20">
@@ -907,16 +931,16 @@
       </c>
       <c r="C20" s="13">
         <f>(C6-C9)/C6</f>
-        <v/>
+        <v>0.15</v>
       </c>
       <c r="D20" s="14" t="inlineStr">
         <is>
           <t>&gt; 15%</t>
         </is>
       </c>
-      <c r="E20" s="15">
+      <c r="E20" s="15" t="str">
         <f>IF(C20&gt;0.15,"✅ Sano",IF(C20&gt;0.1,"⚠️ Ajustado","🔴 Peligro"))</f>
-        <v/>
+        <v>⚠️ Ajustado</v>
       </c>
     </row>
     <row r="21">
@@ -927,7 +951,7 @@
       </c>
       <c r="C21" s="16">
         <f>C9/C10</f>
-        <v/>
+        <v>22.578125</v>
       </c>
       <c r="D21" s="14" t="inlineStr">
         <is>
@@ -944,7 +968,7 @@
       </c>
       <c r="C22" s="16">
         <f>C6/(C11*C12)</f>
-        <v/>
+        <v>2.951388888888889</v>
       </c>
       <c r="D22" s="14" t="inlineStr">
         <is>
@@ -961,7 +985,7 @@
       </c>
       <c r="C23" s="16">
         <f>C6/C10</f>
-        <v/>
+        <v>26.5625</v>
       </c>
       <c r="D23" s="14" t="inlineStr">
         <is>
@@ -978,7 +1002,7 @@
       </c>
       <c r="C24" s="13">
         <f>(C6-C7)/C6</f>
-        <v/>
+        <v>0.7</v>
       </c>
       <c r="D24" s="14" t="inlineStr">
         <is>
@@ -987,6 +1011,8 @@
       </c>
       <c r="E24" s="15" t="n"/>
     </row>
+    <row r="25"/>
+    <row r="26"/>
     <row r="27">
       <c r="A27" s="10" t="inlineStr">
         <is>
@@ -1000,7 +1026,16 @@
     <mergeCell ref="A27:E27"/>
     <mergeCell ref="B1:E1"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1009,16 +1044,16 @@
   <sheetPr>
     <tabColor rgb="00FFD700"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col customWidth="1" max="1" min="1" width="3"/>
-    <col customWidth="1" max="2" min="2" width="35"/>
-    <col customWidth="1" max="3" min="3" width="18"/>
-    <col customWidth="1" max="4" min="4" width="18"/>
-    <col customWidth="1" max="5" min="5" width="18"/>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="35" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1028,6 +1063,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="7" t="inlineStr"/>
       <c r="B3" s="7" t="inlineStr">
@@ -1227,6 +1263,8 @@
         </is>
       </c>
     </row>
+    <row r="12"/>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="10" t="inlineStr">
         <is>
@@ -1239,6 +1277,15 @@
     <mergeCell ref="B1:E1"/>
     <mergeCell ref="A14:E14"/>
   </mergeCells>
-  <pageMargins bottom="1" footer="0.5" header="0.5" left="0.75" right="0.75" top="1"/>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/astro-site/public/dl/kit-plan-financiero/06-dashboard-ratios-financieros.xlsx
+++ b/astro-site/public/dl/kit-plan-financiero/06-dashboard-ratios-financieros.xlsx
@@ -25,7 +25,7 @@
     <numFmt numFmtId="164" formatCode="#,##0.00 €"/>
     <numFmt numFmtId="165" formatCode="0.0%"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -94,8 +94,25 @@
       <color rgb="001565C0"/>
       <sz val="11"/>
     </font>
+    <font>
+      <b val="1"/>
+      <color rgb="009C6500"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <i val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <sz val="8"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="12">
     <fill>
       <patternFill/>
     </fill>
@@ -132,6 +149,31 @@
         <bgColor rgb="00FFCDD2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="002D2D2D"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C8E6C9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFF9C4"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFCDD2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00E8F5E9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -159,7 +201,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -200,10 +242,111 @@
     <xf numFmtId="0" fontId="8" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="11" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="11" borderId="1" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -274,6 +417,155 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <style val="10"/>
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Tu valor vs objetivo del sector</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Ratios'!C16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Ratios'!$B$17:$B$20</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Ratios'!$C$17:$C$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Ratios'!F16</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Ratios'!$B$17:$B$20</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Ratios'!$F$17:$F$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>%</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>41</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="6480000" cy="3240000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -566,11 +858,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="85" customWidth="1" min="2" max="2"/>
+    <col width="100" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -607,7 +899,7 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>▸ Los benchmarks del sector aparecen para comparar tu rendimiento.</t>
+          <t>▸ «Coste de comida — consumo» no son las facturas del mes: es existencias iniciales + compras − existencias finales. El mes que llenas la bodega, las compras se disparan y el consumo no.</t>
         </is>
       </c>
     </row>
@@ -629,40 +921,74 @@
     <row r="12">
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>▸ Food Cost ideal: 28-32% sobre ventas.</t>
+          <t>▸ Food Cost %: óptimo &lt; 28% · peligro &gt; 32% (los números viven en Benchmarks!F:G).</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>▸ Labor Cost ideal: 25-30% sobre ventas.</t>
+          <t>▸ Labor Cost %: óptimo &lt; 25% · peligro &gt; 30% (los números viven en Benchmarks!F:G).</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>▸ Prime Cost (Food + Labor): máximo 60-65%.</t>
+          <t>▸ Prime Cost %: óptimo &lt; 60% · peligro &gt; 65% (los números viven en Benchmarks!F:G).</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>▸ GOP (Gross Operating Profit): objetivo &gt;15%.</t>
+          <t>▸ GOP %: óptimo &gt; 20% · peligro &lt; 15% (los números viven en Benchmarks!F:G).</t>
         </is>
       </c>
     </row>
     <row r="16"/>
     <row r="17">
-      <c r="B17" s="4" t="inlineStr">
-        <is>
-          <t>Versión 1.1 · agosto 2026 · aichef.pro/kit-plan-financiero · info@aichef.pro</t>
+      <c r="B17" s="4" t="n"/>
+    </row>
+    <row r="18"/>
+    <row r="19">
+      <c r="B19" s="4" t="inlineStr">
+        <is>
+          <t>▸ El RevPASH se mide por PLAZA y hora (aforo × horas de servicio), no por m². «Horas de servicio» son aquellas en las que hay clientes sentados (p. ej. 6 h/día × 26 días = 156), no las que el local está abierto. Las ventas por m² tienen su propia fila.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20"/>
+    <row r="21">
+      <c r="B21" s="20" t="inlineStr">
+        <is>
+          <t>Todas las cifras van SIN IVA; en el 03 (tesorería) van CON IVA porque es caja.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="20" t="inlineStr">
+        <is>
+          <t>Para editar una celda que no esté en verde: Revisar → Desproteger hoja (no tiene contraseña).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="20" t="inlineStr">
+        <is>
+          <t>Diseñado por John Guerrero — chef y consultor gastronómico desde 2010, en cocina desde los 17 años · johnguerrero.es</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="20" t="inlineStr">
+        <is>
+          <t>Versión 2.0 · agosto 2026 · aichef.pro/kit-plan-financiero · info@aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
@@ -683,347 +1009,1090 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E27"/>
+  <dimension ref="A1:H50"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="3" customWidth="1" min="1" max="1"/>
+    <col width="40" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="30" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="B1" s="5" t="inlineStr">
+        <is>
+          <t>Dashboard de Ratios Financieros</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="B2" s="2" t="inlineStr">
+        <is>
+          <t>AI Chef Pro · aichef.pro — Kit Plan Financiero para Restaurantes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="B3" s="21" t="inlineStr">
+        <is>
+          <t>VALORES DE EJEMPLO — sustitúyelos por los tuyos</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>DATOS DE ENTRADA</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="7" t="inlineStr"/>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>Concepto</t>
+        </is>
+      </c>
+      <c r="C5" s="7" t="inlineStr">
+        <is>
+          <t>Valor</t>
+        </is>
+      </c>
+      <c r="D5" s="7" t="inlineStr">
+        <is>
+          <t>Período</t>
+        </is>
+      </c>
+      <c r="E5" s="7" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="B6" s="8" t="inlineStr">
+        <is>
+          <t>Ventas totales (€, sin IVA)</t>
+        </is>
+      </c>
+      <c r="C6" s="22" t="n">
+        <v>31460</v>
+      </c>
+      <c r="D6" s="10" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>· de las cuales, barra / bebida (€, sin IVA)</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="n">
+        <v>7865</v>
+      </c>
+      <c r="D7" s="10" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="B8" s="8" t="inlineStr">
+        <is>
+          <t>Coste de comida — consumo (€)</t>
+        </is>
+      </c>
+      <c r="C8" s="23">
+        <f>IFERROR($C$33+$C$34-$C$35,0)</f>
+        <v>7078.5</v>
+      </c>
+      <c r="D8" s="10" t="inlineStr">
+        <is>
+          <t>Calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>Gastos operativos totales (€)</t>
+        </is>
+      </c>
+      <c r="C9" s="23">
+        <f>IFERROR($C$8+$C$36+$C$10+$C$37,0)</f>
+        <v>23017.6</v>
+      </c>
+      <c r="D9" s="10" t="inlineStr">
+        <is>
+          <t>Calculado</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="B10" s="8" t="inlineStr">
+        <is>
+          <t>Coste personal total (€)</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="n">
+        <v>8808.799999999999</v>
+      </c>
+      <c r="D10" s="10" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>m² de sala</t>
+        </is>
+      </c>
+      <c r="C11" s="24" t="n">
+        <v>80</v>
+      </c>
+      <c r="D11" s="10" t="n"/>
+    </row>
+    <row r="12">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>Horas de SERVICIO / mes (con clientes sentados)</t>
+        </is>
+      </c>
+      <c r="C12" s="24" t="n">
+        <v>156</v>
+      </c>
+      <c r="D12" s="10" t="n"/>
+    </row>
+    <row r="13">
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>Nº de plazas (aforo)</t>
+        </is>
+      </c>
+      <c r="C13" s="24" t="n">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>Nº de cubiertos servidos</t>
+        </is>
+      </c>
+      <c r="C14" s="24" t="n">
+        <v>1430</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Mensual</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>RATIOS CALCULADOS</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="25" t="n"/>
+      <c r="B16" s="26" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="inlineStr">
+        <is>
+          <t>Tu Valor</t>
+        </is>
+      </c>
+      <c r="D16" s="26" t="inlineStr">
+        <is>
+          <t>Benchmark Sector</t>
+        </is>
+      </c>
+      <c r="E16" s="26" t="inlineStr">
+        <is>
+          <t>Estado</t>
+        </is>
+      </c>
+      <c r="F16" s="27" t="inlineStr">
+        <is>
+          <t>Objetivo</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>Food Cost % (sobre ventas de comida)</t>
+        </is>
+      </c>
+      <c r="C17" s="13">
+        <f>IF(($C$6-$C$7)&lt;=0,"Indica las ventas",$C$8/($C$6-$C$7))</f>
+        <v>0.3</v>
+      </c>
+      <c r="D17" s="28" t="str">
+        <f>Benchmarks!$D$4</f>
+        <v>28% - 32%</v>
+      </c>
+      <c r="E17" s="15" t="str">
+        <f>IFERROR(IF(ISNUMBER($C17),IF($C17&lt;Benchmarks!$F$4,"✅ Excelente",IF($C17&lt;=Benchmarks!$G$4,"⚠️ Aceptable","🔴 Alto")),"—"),"—")</f>
+        <v>⚠️ Aceptable</v>
+      </c>
+      <c r="F17" s="29">
+        <f>Benchmarks!$F$4</f>
+        <v>0.28</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>Labor Cost %</t>
+        </is>
+      </c>
+      <c r="C18" s="13">
+        <f>IFERROR($C$10/$C$6,"Indica las ventas")</f>
+        <v>0.27999999999999997</v>
+      </c>
+      <c r="D18" s="28" t="str">
+        <f>Benchmarks!$D$5</f>
+        <v>25% - 30%</v>
+      </c>
+      <c r="E18" s="15" t="str">
+        <f>IFERROR(IF(ISNUMBER($C18),IF($C18&lt;Benchmarks!$F$5,"✅ Excelente",IF($C18&lt;=Benchmarks!$G$5,"⚠️ Aceptable","🔴 Alto")),"—"),"—")</f>
+        <v>⚠️ Aceptable</v>
+      </c>
+      <c r="F18" s="29">
+        <f>Benchmarks!$F$5</f>
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="B19" s="8" t="inlineStr">
+        <is>
+          <t>Prime Cost % (comida + bebida + personal)</t>
+        </is>
+      </c>
+      <c r="C19" s="13">
+        <f>IFERROR(($C$8+$C$36+$C$10)/$C$6,"Indica las ventas")</f>
+        <v>0.5599999999999999</v>
+      </c>
+      <c r="D19" s="28" t="str">
+        <f>Benchmarks!$D$6</f>
+        <v>60% - 65%</v>
+      </c>
+      <c r="E19" s="15" t="str">
+        <f>IFERROR(IF(ISNUMBER($C19),IF($C19&lt;Benchmarks!$F$6,"✅ Excelente",IF($C19&lt;=Benchmarks!$G$6,"⚠️ Aceptable","🔴 Alto")),"—"),"—")</f>
+        <v>✅ Excelente</v>
+      </c>
+      <c r="F19" s="29">
+        <f>Benchmarks!$F$6</f>
+        <v>0.6</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="8" t="inlineStr">
+        <is>
+          <t>GOP (Gross Operating Profit) %</t>
+        </is>
+      </c>
+      <c r="C20" s="13">
+        <f>IFERROR(($C$6-$C$9)/$C$6,"Indica las ventas")</f>
+        <v>0.26835346471710114</v>
+      </c>
+      <c r="D20" s="28" t="str">
+        <f>Benchmarks!$D$7</f>
+        <v>15% - 20%</v>
+      </c>
+      <c r="E20" s="15" t="str">
+        <f>IFERROR(IF(ISNUMBER($C20),IF($C20&gt;Benchmarks!$F$7,"✅ Sano",IF($C20&gt;=Benchmarks!$G$7,"⚠️ Ajustado","🔴 Peligro")),"—"),"—")</f>
+        <v>✅ Sano</v>
+      </c>
+      <c r="F20" s="29">
+        <f>Benchmarks!$F$7</f>
+        <v>0.2</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="8" t="inlineStr">
+        <is>
+          <t>Beverage Cost % (sobre ventas de barra)</t>
+        </is>
+      </c>
+      <c r="C21" s="13">
+        <f>IFERROR($C$36/$C$7,"Indica las ventas de barra")</f>
+        <v>0.22</v>
+      </c>
+      <c r="D21" s="28" t="str">
+        <f>Benchmarks!$D$12</f>
+        <v>18% - 24%</v>
+      </c>
+      <c r="E21" s="15" t="str">
+        <f>IFERROR(IF(ISNUMBER($C21),IF($C21&lt;Benchmarks!$F$12,"✅ Excelente",IF($C21&lt;=Benchmarks!$G$12,"⚠️ Aceptable","🔴 Alto")),"—"),"—")</f>
+        <v>⚠️ Aceptable</v>
+      </c>
+      <c r="F21" s="29">
+        <f>Benchmarks!$F$12</f>
+        <v>0.18</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="B22" s="8" t="inlineStr">
+        <is>
+          <t>RevPASH (€/plaza/hora)</t>
+        </is>
+      </c>
+      <c r="C22" s="16">
+        <f>IFERROR($C$6/($C$13*$C$12),"Indica plazas y horas")</f>
+        <v>3.361111111111111</v>
+      </c>
+      <c r="D22" s="28" t="str">
+        <f>Benchmarks!$D$13</f>
+        <v>3€ - 6€</v>
+      </c>
+      <c r="E22" s="15" t="str">
+        <f>IFERROR(IF(ISNUMBER($C22),IF($C22&gt;Benchmarks!$F$13,"✅ Sano",IF($C22&gt;=Benchmarks!$G$13,"⚠️ Ajustado","🔴 Peligro")),"—"),"—")</f>
+        <v>⚠️ Ajustado</v>
+      </c>
+      <c r="F22" s="30">
+        <f>Benchmarks!$F$13</f>
+        <v>6.0</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="8" t="inlineStr">
+        <is>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="C23" s="13">
+        <f>IFERROR(($C$6-$C$9-$C$38)/$C$6,"Indica las ventas")</f>
+        <v>0.17299427844882395</v>
+      </c>
+      <c r="D23" s="28" t="str">
+        <f>Benchmarks!$D$10</f>
+        <v>10% - 15%</v>
+      </c>
+      <c r="E23" s="15" t="str">
+        <f>IFERROR(IF(ISNUMBER($C23),IF($C23&gt;Benchmarks!$F$10,"✅ Sano",IF($C23&gt;=Benchmarks!$G$10,"⚠️ Ajustado","🔴 Peligro")),"—"),"—")</f>
+        <v>✅ Sano</v>
+      </c>
+      <c r="F23" s="29">
+        <f>Benchmarks!$F$10</f>
+        <v>0.15</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="8" t="inlineStr">
+        <is>
+          <t>Coste por cubierto / Ticket medio</t>
+        </is>
+      </c>
+      <c r="C24" s="13">
+        <f>IFERROR($C$28/$C$29,"Indica los cubiertos")</f>
+        <v>0.7316465352828989</v>
+      </c>
+      <c r="D24" s="28" t="str">
+        <f>Benchmarks!$D$11</f>
+        <v>80% - 85%</v>
+      </c>
+      <c r="E24" s="15" t="str">
+        <f>IFERROR(IF(ISNUMBER($C24),IF($C24&lt;Benchmarks!$F$11,"✅ Excelente",IF($C24&lt;=Benchmarks!$G$11,"⚠️ Aceptable","🔴 Alto")),"—"),"—")</f>
+        <v>✅ Excelente</v>
+      </c>
+      <c r="F24" s="29">
+        <f>Benchmarks!$F$11</f>
+        <v>0.8</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="B25" s="8" t="inlineStr">
+        <is>
+          <t>Margen bruto %</t>
+        </is>
+      </c>
+      <c r="C25" s="29">
+        <f>IFERROR(($C$6-$C$8-$C$36)/$C$6,"Indica las ventas")</f>
+        <v>0.72</v>
+      </c>
+      <c r="D25" s="31" t="str">
+        <f>Benchmarks!$D$14</f>
+        <v>65% - 70%</v>
+      </c>
+      <c r="E25" t="str">
+        <f>IFERROR(IF(ISNUMBER($C25),IF($C25&gt;Benchmarks!$F$14,"✅ Sano",IF($C25&gt;=Benchmarks!$G$14,"⚠️ Ajustado","🔴 Peligro")),"—"),"—")</f>
+        <v>✅ Sano</v>
+      </c>
+      <c r="F25" s="29">
+        <f>Benchmarks!$F$14</f>
+        <v>0.7</v>
+      </c>
+    </row>
+    <row r="26"/>
+    <row r="27">
+      <c r="A27" s="10" t="n"/>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>OTROS INDICADORES</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="B28" s="8" t="inlineStr">
+        <is>
+          <t>Coste por cubierto (€)</t>
+        </is>
+      </c>
+      <c r="C28" s="30">
+        <f>IFERROR($C$9/$C$14,"Indica los cubiertos")</f>
+        <v>16.096223776223777</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="8" t="inlineStr">
+        <is>
+          <t>Ticket medio (€, sin IVA)</t>
+        </is>
+      </c>
+      <c r="C29" s="30">
+        <f>IFERROR($C$6/$C$14,"Indica los cubiertos")</f>
+        <v>22.0</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="8" t="inlineStr">
+        <is>
+          <t>Ventas por m² de sala (€, sin IVA)</t>
+        </is>
+      </c>
+      <c r="C30" s="30">
+        <f>IFERROR($C$6/$C$11,"Indica los m² de sala")</f>
+        <v>393.25</v>
+      </c>
+    </row>
+    <row r="31"/>
+    <row r="32">
+      <c r="B32" s="6" t="inlineStr">
+        <is>
+          <t>DATOS COMPLEMENTARIOS (existencias y desglose de gastos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="8" t="inlineStr">
+        <is>
+          <t>Existencias iniciales de comida (€)</t>
+        </is>
+      </c>
+      <c r="C33" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D33" s="32" t="inlineStr">
+        <is>
+          <t>Lo que había en despensa y cámara el día 1.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="B34" s="8" t="inlineStr">
+        <is>
+          <t>Compras de comida del período (€)</t>
+        </is>
+      </c>
+      <c r="C34" s="22" t="n">
+        <v>7078.5</v>
+      </c>
+      <c r="D34" s="32" t="inlineStr">
+        <is>
+          <t>Facturas de alimentación del período.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="8" t="inlineStr">
+        <is>
+          <t>Existencias finales de comida (€)</t>
+        </is>
+      </c>
+      <c r="C35" s="22" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="32" t="inlineStr">
+        <is>
+          <t>Consumo = iniciales + compras − finales. El mes del pedido grande, las compras se disparan y el consumo NO.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="8" t="inlineStr">
+        <is>
+          <t>Coste de bebida — consumo (€)</t>
+        </is>
+      </c>
+      <c r="C36" s="22" t="n">
+        <v>1730.3</v>
+      </c>
+      <c r="D36" s="32" t="inlineStr">
+        <is>
+          <t>Barra y bodega, aparte de la comida.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="B37" s="8" t="inlineStr">
+        <is>
+          <t>Otros gastos operativos (€)</t>
+        </is>
+      </c>
+      <c r="C37" s="22" t="n">
+        <v>5400</v>
+      </c>
+      <c r="D37" s="32" t="inlineStr">
+        <is>
+          <t>Suministros, marketing, gestoría, comisiones de delivery… SIN alquiler ni amortización (van aparte, USALI). Con este valor el EBITDA del ejemplo sale al 17,3 %, el mismo que dan el 02 y el BONUS-08.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="8" t="inlineStr">
+        <is>
+          <t>Alquiler (€)</t>
+        </is>
+      </c>
+      <c r="C38" s="22" t="n">
+        <v>3000</v>
+      </c>
+      <c r="D38" s="32" t="inlineStr">
+        <is>
+          <t>Fuera del GOP: en USALI es carga de propiedad.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39"/>
+    <row r="40">
+      <c r="B40" s="32" t="inlineStr">
+        <is>
+          <t>El GOP se mide ANTES del alquiler y de la amortización (criterio USALI): por eso el alquiler tiene su propia línea y el EBITDA % se calcula aparte.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41"/>
+    <row r="42"/>
+    <row r="43"/>
+    <row r="44"/>
+    <row r="45"/>
+    <row r="46"/>
+    <row r="47"/>
+    <row r="48"/>
+    <row r="49"/>
+    <row r="50">
+      <c r="A50" s="33" t="inlineStr">
+        <is>
+          <t>© 2026 AI Chef Pro · aichef.pro</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="2">
+    <mergeCell ref="B2:E2"/>
+    <mergeCell ref="B1:E1"/>
+  </mergeCells>
+  <conditionalFormatting sqref="E17:E25">
+    <cfRule type="containsText" priority="1" operator="containsText" dxfId="0" stopIfTrue="1" text="🔴 Alto">
+      <formula>NOT(ISERROR(SEARCH("🔴 Alto",E17)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="2" operator="containsText" dxfId="1" stopIfTrue="1" text="⚠️ Aceptable">
+      <formula>NOT(ISERROR(SEARCH("⚠️ Aceptable",E17)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="3" operator="containsText" dxfId="2" stopIfTrue="1" text="✅ Excelente">
+      <formula>NOT(ISERROR(SEARCH("✅ Excelente",E17)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="4" operator="containsText" dxfId="0" stopIfTrue="1" text="🔴 Peligro">
+      <formula>NOT(ISERROR(SEARCH("🔴 Peligro",E17)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="5" operator="containsText" dxfId="1" stopIfTrue="1" text="⚠️ Ajustado">
+      <formula>NOT(ISERROR(SEARCH("⚠️ Ajustado",E17)))</formula>
+    </cfRule>
+    <cfRule type="containsText" priority="6" operator="containsText" dxfId="2" stopIfTrue="1" text="✅ Sano">
+      <formula>NOT(ISERROR(SEARCH("✅ Sano",E17)))</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <dataValidations count="1">
+    <dataValidation sqref="C6 C7 C10 C11 C12 C13 C14 C33 C34 C35 C36 C37 C38" showDropDown="0" showInputMessage="0" showErrorMessage="1" allowBlank="1" errorTitle="Importe no válido" error="Escribe un número mayor o igual que 0." type="decimal" operator="greaterThanOrEqual">
+      <formula1>0</formula1>
+    </dataValidation>
+  </dataValidations>
+  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader/>
+    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <tabColor rgb="00FFD700"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:H20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
     <col width="35" customWidth="1" min="2" max="2"/>
     <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
     <col width="18" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="B1" s="5" t="inlineStr">
         <is>
-          <t>Dashboard de Ratios Financieros</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="B2" s="2" t="inlineStr">
-        <is>
-          <t>AI Chef Pro · aichef.pro — Kit Plan Financiero para Restaurantes</t>
-        </is>
-      </c>
-    </row>
-    <row r="3"/>
+          <t>Benchmarks del Sector Hostelería</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" s="25" t="n"/>
+      <c r="B3" s="34" t="inlineStr">
+        <is>
+          <t>Ratio</t>
+        </is>
+      </c>
+      <c r="C3" s="34" t="inlineStr">
+        <is>
+          <t>Óptimo</t>
+        </is>
+      </c>
+      <c r="D3" s="34" t="inlineStr">
+        <is>
+          <t>Aceptable</t>
+        </is>
+      </c>
+      <c r="E3" s="34" t="inlineStr">
+        <is>
+          <t>Peligro</t>
+        </is>
+      </c>
+      <c r="F3" s="35" t="inlineStr">
+        <is>
+          <t>Óptimo (nº)</t>
+        </is>
+      </c>
+      <c r="G3" s="35" t="inlineStr">
+        <is>
+          <t>Límite (nº)</t>
+        </is>
+      </c>
+      <c r="H3" s="35" t="inlineStr">
+        <is>
+          <t>Sentido</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>DATOS DE ENTRADA</t>
+      <c r="B4" s="8" t="inlineStr">
+        <is>
+          <t>Food Cost %</t>
+        </is>
+      </c>
+      <c r="C4" s="36" t="inlineStr">
+        <is>
+          <t>&lt; 28%</t>
+        </is>
+      </c>
+      <c r="D4" s="37" t="inlineStr">
+        <is>
+          <t>28% - 32%</t>
+        </is>
+      </c>
+      <c r="E4" s="38" t="inlineStr">
+        <is>
+          <t>&gt; 32%</t>
+        </is>
+      </c>
+      <c r="F4" s="29" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="G4" s="29" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="H4" s="39" t="inlineStr">
+        <is>
+          <t>menor es mejor</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="7" t="inlineStr"/>
-      <c r="B5" s="7" t="inlineStr">
-        <is>
-          <t>Concepto</t>
-        </is>
-      </c>
-      <c r="C5" s="7" t="inlineStr">
-        <is>
-          <t>Valor</t>
-        </is>
-      </c>
-      <c r="D5" s="7" t="inlineStr">
-        <is>
-          <t>Período</t>
-        </is>
-      </c>
-      <c r="E5" s="7" t="inlineStr"/>
+      <c r="B5" s="8" t="inlineStr">
+        <is>
+          <t>Labor Cost %</t>
+        </is>
+      </c>
+      <c r="C5" s="36" t="inlineStr">
+        <is>
+          <t>&lt; 25%</t>
+        </is>
+      </c>
+      <c r="D5" s="37" t="inlineStr">
+        <is>
+          <t>25% - 30%</t>
+        </is>
+      </c>
+      <c r="E5" s="38" t="inlineStr">
+        <is>
+          <t>&gt; 30%</t>
+        </is>
+      </c>
+      <c r="F5" s="29" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="G5" s="29" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="H5" s="39" t="inlineStr">
+        <is>
+          <t>menor es mejor</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="B6" s="8" t="inlineStr">
         <is>
-          <t>Ventas totales (€)</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="n">
-        <v>85000</v>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>Mensual</t>
+          <t>Prime Cost %</t>
+        </is>
+      </c>
+      <c r="C6" s="36" t="inlineStr">
+        <is>
+          <t>&lt; 60%</t>
+        </is>
+      </c>
+      <c r="D6" s="37" t="inlineStr">
+        <is>
+          <t>60% - 65%</t>
+        </is>
+      </c>
+      <c r="E6" s="38" t="inlineStr">
+        <is>
+          <t>&gt; 65%</t>
+        </is>
+      </c>
+      <c r="F6" s="29" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="G6" s="29" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H6" s="39" t="inlineStr">
+        <is>
+          <t>menor es mejor</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="B7" s="8" t="inlineStr">
         <is>
-          <t>Coste materia prima (€)</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="n">
-        <v>25500</v>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>Mensual</t>
+          <t>GOP %</t>
+        </is>
+      </c>
+      <c r="C7" s="36" t="inlineStr">
+        <is>
+          <t>&gt; 20%</t>
+        </is>
+      </c>
+      <c r="D7" s="37" t="inlineStr">
+        <is>
+          <t>15% - 20%</t>
+        </is>
+      </c>
+      <c r="E7" s="38" t="inlineStr">
+        <is>
+          <t>&lt; 15%</t>
+        </is>
+      </c>
+      <c r="F7" s="29" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="G7" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="H7" s="39" t="inlineStr">
+        <is>
+          <t>mayor es mejor</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="B8" s="8" t="inlineStr">
         <is>
-          <t>Coste personal total (€)</t>
-        </is>
-      </c>
-      <c r="C8" s="9" t="n">
-        <v>23800</v>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>Mensual</t>
+          <t>Alquiler / Ventas</t>
+        </is>
+      </c>
+      <c r="C8" s="36" t="inlineStr">
+        <is>
+          <t>&lt; 8%</t>
+        </is>
+      </c>
+      <c r="D8" s="37" t="inlineStr">
+        <is>
+          <t>8% - 12%</t>
+        </is>
+      </c>
+      <c r="E8" s="38" t="inlineStr">
+        <is>
+          <t>&gt; 12%</t>
+        </is>
+      </c>
+      <c r="F8" s="29" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="G8" s="29" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H8" s="39" t="inlineStr">
+        <is>
+          <t>menor es mejor</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="B9" s="8" t="inlineStr">
         <is>
-          <t>Gastos operativos totales (€)</t>
-        </is>
-      </c>
-      <c r="C9" s="9" t="n">
-        <v>72250</v>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>Mensual</t>
+          <t>Marketing / Ventas</t>
+        </is>
+      </c>
+      <c r="C9" s="36" t="inlineStr">
+        <is>
+          <t>&lt; 5%</t>
+        </is>
+      </c>
+      <c r="D9" s="37" t="inlineStr">
+        <is>
+          <t>5% - 8%</t>
+        </is>
+      </c>
+      <c r="E9" s="38" t="inlineStr">
+        <is>
+          <t>&gt; 8%</t>
+        </is>
+      </c>
+      <c r="F9" s="29" t="n">
+        <v>0.05</v>
+      </c>
+      <c r="G9" s="29" t="n">
+        <v>0.08</v>
+      </c>
+      <c r="H9" s="39" t="inlineStr">
+        <is>
+          <t>menor es mejor</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="B10" s="8" t="inlineStr">
         <is>
-          <t>Nº de cubiertos servidos</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="n">
-        <v>3200</v>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>Mensual</t>
+          <t>EBITDA %</t>
+        </is>
+      </c>
+      <c r="C10" s="36" t="inlineStr">
+        <is>
+          <t>&gt; 15%</t>
+        </is>
+      </c>
+      <c r="D10" s="37" t="inlineStr">
+        <is>
+          <t>10% - 15%</t>
+        </is>
+      </c>
+      <c r="E10" s="38" t="inlineStr">
+        <is>
+          <t>&lt; 10%</t>
+        </is>
+      </c>
+      <c r="F10" s="29" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="G10" s="29" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="H10" s="39" t="inlineStr">
+        <is>
+          <t>mayor es mejor</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" s="8" t="inlineStr">
         <is>
-          <t>m² de sala</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="n">
-        <v>80</v>
-      </c>
-      <c r="D11" s="10" t="inlineStr"/>
+          <t>Coste cubierto / Ticket</t>
+        </is>
+      </c>
+      <c r="C11" s="36" t="inlineStr">
+        <is>
+          <t>&lt; 80%</t>
+        </is>
+      </c>
+      <c r="D11" s="37" t="inlineStr">
+        <is>
+          <t>80% - 85%</t>
+        </is>
+      </c>
+      <c r="E11" s="38" t="inlineStr">
+        <is>
+          <t>&gt; 85%</t>
+        </is>
+      </c>
+      <c r="F11" s="29" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="G11" s="29" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="H11" s="39" t="inlineStr">
+        <is>
+          <t>menor es mejor</t>
+        </is>
+      </c>
     </row>
     <row r="12">
-      <c r="B12" s="8" t="inlineStr">
-        <is>
-          <t>Horas de servicio / mes</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="n">
-        <v>360</v>
-      </c>
-      <c r="D12" s="10" t="inlineStr"/>
-    </row>
-    <row r="13"/>
-    <row r="14"/>
-    <row r="15">
-      <c r="B15" s="6" t="inlineStr">
-        <is>
-          <t>RATIOS CALCULADOS</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="7" t="inlineStr"/>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>Ratio</t>
-        </is>
-      </c>
-      <c r="C16" s="7" t="inlineStr">
-        <is>
-          <t>Tu Valor</t>
-        </is>
-      </c>
-      <c r="D16" s="7" t="inlineStr">
-        <is>
-          <t>Benchmark Sector</t>
-        </is>
-      </c>
-      <c r="E16" s="7" t="inlineStr">
-        <is>
-          <t>Estado</t>
-        </is>
-      </c>
-    </row>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Beverage Cost %</t>
+        </is>
+      </c>
+      <c r="C12" s="40" t="inlineStr">
+        <is>
+          <t>&lt; 18%</t>
+        </is>
+      </c>
+      <c r="D12" s="41" t="inlineStr">
+        <is>
+          <t>18% - 24%</t>
+        </is>
+      </c>
+      <c r="E12" s="42" t="inlineStr">
+        <is>
+          <t>&gt; 24%</t>
+        </is>
+      </c>
+      <c r="F12" s="29" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G12" s="29" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="H12" s="39" t="inlineStr">
+        <is>
+          <t>menor es mejor</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>RevPASH (€/plaza/hora)</t>
+        </is>
+      </c>
+      <c r="C13" s="40" t="inlineStr">
+        <is>
+          <t>&gt; 6€</t>
+        </is>
+      </c>
+      <c r="D13" s="41" t="inlineStr">
+        <is>
+          <t>3€ - 6€</t>
+        </is>
+      </c>
+      <c r="E13" s="42" t="inlineStr">
+        <is>
+          <t>&lt; 3€</t>
+        </is>
+      </c>
+      <c r="F13" s="30" t="n">
+        <v>6</v>
+      </c>
+      <c r="G13" s="30" t="n">
+        <v>3</v>
+      </c>
+      <c r="H13" s="39" t="inlineStr">
+        <is>
+          <t>mayor es mejor</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="10" t="n"/>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Margen bruto %</t>
+        </is>
+      </c>
+      <c r="C14" s="40" t="inlineStr">
+        <is>
+          <t>&gt; 70%</t>
+        </is>
+      </c>
+      <c r="D14" s="41" t="inlineStr">
+        <is>
+          <t>65% - 70%</t>
+        </is>
+      </c>
+      <c r="E14" s="42" t="inlineStr">
+        <is>
+          <t>&lt; 65%</t>
+        </is>
+      </c>
+      <c r="F14" s="29" t="n">
+        <v>0.7</v>
+      </c>
+      <c r="G14" s="29" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="H14" s="39" t="inlineStr">
+        <is>
+          <t>mayor es mejor</t>
+        </is>
+      </c>
+    </row>
+    <row r="15"/>
+    <row r="16"/>
     <row r="17">
-      <c r="B17" s="12" t="inlineStr">
-        <is>
-          <t>Food Cost %</t>
-        </is>
-      </c>
-      <c r="C17" s="13">
-        <f>C7/C6</f>
-        <v>0.3</v>
-      </c>
-      <c r="D17" s="14" t="inlineStr">
-        <is>
-          <t>28% - 32%</t>
-        </is>
-      </c>
-      <c r="E17" s="15" t="str">
-        <f>IF(C17&lt;0.28,"✅ Excelente",IF(C17&lt;0.33,"⚠️ Aceptable","🔴 Alto"))</f>
-        <v>⚠️ Aceptable</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="12" t="inlineStr">
-        <is>
-          <t>Labor Cost %</t>
-        </is>
-      </c>
-      <c r="C18" s="13">
-        <f>C8/C6</f>
-        <v>0.28</v>
-      </c>
-      <c r="D18" s="14" t="inlineStr">
-        <is>
-          <t>25% - 30%</t>
-        </is>
-      </c>
-      <c r="E18" s="15" t="str">
-        <f>IF(C18&lt;0.25,"✅ Excelente",IF(C18&lt;0.31,"⚠️ Aceptable","🔴 Alto"))</f>
-        <v>⚠️ Aceptable</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="B19" s="12" t="inlineStr">
-        <is>
-          <t>Prime Cost % (Food + Labor)</t>
-        </is>
-      </c>
-      <c r="C19" s="13">
-        <f>(C7+C8)/C6</f>
-        <v>0.58</v>
-      </c>
-      <c r="D19" s="14" t="inlineStr">
-        <is>
-          <t>&lt; 65%</t>
-        </is>
-      </c>
-      <c r="E19" s="15" t="str">
-        <f>IF(C19&lt;0.6,"✅ Excelente",IF(C19&lt;0.66,"⚠️ Aceptable","🔴 Alto"))</f>
-        <v>✅ Excelente</v>
-      </c>
-    </row>
+      <c r="B17" s="32" t="inlineStr">
+        <is>
+          <t>Las columnas «Óptimo (nº)» y «Límite (nº)» son la ÚNICA fuente de umbrales del kit: el semáforo de la pestaña Ratios las lee, y los textos de la izquierda se generan desde ellas. Edítalas y todo el dashboard se mueve con ellas.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18"/>
+    <row r="19"/>
     <row r="20">
-      <c r="B20" s="12" t="inlineStr">
-        <is>
-          <t>GOP (Gross Operating Profit) %</t>
-        </is>
-      </c>
-      <c r="C20" s="13">
-        <f>(C6-C9)/C6</f>
-        <v>0.15</v>
-      </c>
-      <c r="D20" s="14" t="inlineStr">
-        <is>
-          <t>&gt; 15%</t>
-        </is>
-      </c>
-      <c r="E20" s="15" t="str">
-        <f>IF(C20&gt;0.15,"✅ Sano",IF(C20&gt;0.1,"⚠️ Ajustado","🔴 Peligro"))</f>
-        <v>⚠️ Ajustado</v>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="12" t="inlineStr">
-        <is>
-          <t>Coste por cubierto (€)</t>
-        </is>
-      </c>
-      <c r="C21" s="16">
-        <f>C9/C10</f>
-        <v>22.578125</v>
-      </c>
-      <c r="D21" s="14" t="inlineStr">
-        <is>
-          <t>Varía por concepto</t>
-        </is>
-      </c>
-      <c r="E21" s="15" t="n"/>
-    </row>
-    <row r="22">
-      <c r="B22" s="12" t="inlineStr">
-        <is>
-          <t>RevPASH (€/m²/hora)</t>
-        </is>
-      </c>
-      <c r="C22" s="16">
-        <f>C6/(C11*C12)</f>
-        <v>2.951388888888889</v>
-      </c>
-      <c r="D22" s="14" t="inlineStr">
-        <is>
-          <t>&gt; 8€ casual dining</t>
-        </is>
-      </c>
-      <c r="E22" s="15" t="n"/>
-    </row>
-    <row r="23">
-      <c r="B23" s="12" t="inlineStr">
-        <is>
-          <t>Ticket medio (€)</t>
-        </is>
-      </c>
-      <c r="C23" s="16">
-        <f>C6/C10</f>
-        <v>26.5625</v>
-      </c>
-      <c r="D23" s="14" t="inlineStr">
-        <is>
-          <t>Varía por concepto</t>
-        </is>
-      </c>
-      <c r="E23" s="15" t="n"/>
-    </row>
-    <row r="24">
-      <c r="B24" s="12" t="inlineStr">
-        <is>
-          <t>Margen bruto %</t>
-        </is>
-      </c>
-      <c r="C24" s="13">
-        <f>(C6-C7)/C6</f>
-        <v>0.7</v>
-      </c>
-      <c r="D24" s="14" t="inlineStr">
-        <is>
-          <t>&gt; 65%</t>
-        </is>
-      </c>
-      <c r="E24" s="15" t="n"/>
-    </row>
-    <row r="25"/>
-    <row r="26"/>
-    <row r="27">
-      <c r="A27" s="10" t="inlineStr">
+      <c r="A20" s="33" t="inlineStr">
         <is>
           <t>© 2026 AI Chef Pro · aichef.pro</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
-    <mergeCell ref="B2:E2"/>
-    <mergeCell ref="A27:E27"/>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="0" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="0"/>
+  <mergeCells count="1">
     <mergeCell ref="B1:E1"/>
   </mergeCells>
   <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
@@ -1037,255 +2106,4 @@
     <firstFooter/>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00FFD700"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:E14"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="3" customWidth="1" min="1" max="1"/>
-    <col width="35" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="18" customWidth="1" min="4" max="4"/>
-    <col width="18" customWidth="1" min="5" max="5"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="B1" s="5" t="inlineStr">
-        <is>
-          <t>Benchmarks del Sector Hostelería</t>
-        </is>
-      </c>
-    </row>
-    <row r="2"/>
-    <row r="3">
-      <c r="A3" s="7" t="inlineStr"/>
-      <c r="B3" s="7" t="inlineStr">
-        <is>
-          <t>Ratio</t>
-        </is>
-      </c>
-      <c r="C3" s="7" t="inlineStr">
-        <is>
-          <t>Óptimo</t>
-        </is>
-      </c>
-      <c r="D3" s="7" t="inlineStr">
-        <is>
-          <t>Aceptable</t>
-        </is>
-      </c>
-      <c r="E3" s="7" t="inlineStr">
-        <is>
-          <t>Peligro</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="B4" s="8" t="inlineStr">
-        <is>
-          <t>Food Cost %</t>
-        </is>
-      </c>
-      <c r="C4" s="17" t="inlineStr">
-        <is>
-          <t>&lt; 28%</t>
-        </is>
-      </c>
-      <c r="D4" s="18" t="inlineStr">
-        <is>
-          <t>28% - 33%</t>
-        </is>
-      </c>
-      <c r="E4" s="19" t="inlineStr">
-        <is>
-          <t>&gt; 33%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="B5" s="8" t="inlineStr">
-        <is>
-          <t>Labor Cost %</t>
-        </is>
-      </c>
-      <c r="C5" s="17" t="inlineStr">
-        <is>
-          <t>&lt; 25%</t>
-        </is>
-      </c>
-      <c r="D5" s="18" t="inlineStr">
-        <is>
-          <t>25% - 30%</t>
-        </is>
-      </c>
-      <c r="E5" s="19" t="inlineStr">
-        <is>
-          <t>&gt; 30%</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="B6" s="8" t="inlineStr">
-        <is>
-          <t>Prime Cost %</t>
-        </is>
-      </c>
-      <c r="C6" s="17" t="inlineStr">
-        <is>
-          <t>&lt; 60%</t>
-        </is>
-      </c>
-      <c r="D6" s="18" t="inlineStr">
-        <is>
-          <t>60% - 65%</t>
-        </is>
-      </c>
-      <c r="E6" s="19" t="inlineStr">
-        <is>
-          <t>&gt; 65%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="B7" s="8" t="inlineStr">
-        <is>
-          <t>GOP %</t>
-        </is>
-      </c>
-      <c r="C7" s="17" t="inlineStr">
-        <is>
-          <t>&gt; 20%</t>
-        </is>
-      </c>
-      <c r="D7" s="18" t="inlineStr">
-        <is>
-          <t>15% - 20%</t>
-        </is>
-      </c>
-      <c r="E7" s="19" t="inlineStr">
-        <is>
-          <t>&lt; 15%</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="B8" s="8" t="inlineStr">
-        <is>
-          <t>Alquiler / Ventas</t>
-        </is>
-      </c>
-      <c r="C8" s="17" t="inlineStr">
-        <is>
-          <t>&lt; 8%</t>
-        </is>
-      </c>
-      <c r="D8" s="18" t="inlineStr">
-        <is>
-          <t>8% - 12%</t>
-        </is>
-      </c>
-      <c r="E8" s="19" t="inlineStr">
-        <is>
-          <t>&gt; 12%</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="B9" s="8" t="inlineStr">
-        <is>
-          <t>Marketing / Ventas</t>
-        </is>
-      </c>
-      <c r="C9" s="17" t="inlineStr">
-        <is>
-          <t>3% - 5%</t>
-        </is>
-      </c>
-      <c r="D9" s="18" t="inlineStr">
-        <is>
-          <t>5% - 8%</t>
-        </is>
-      </c>
-      <c r="E9" s="19" t="inlineStr">
-        <is>
-          <t>&gt; 8%</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="B10" s="8" t="inlineStr">
-        <is>
-          <t>EBITDA %</t>
-        </is>
-      </c>
-      <c r="C10" s="17" t="inlineStr">
-        <is>
-          <t>&gt; 15%</t>
-        </is>
-      </c>
-      <c r="D10" s="18" t="inlineStr">
-        <is>
-          <t>10% - 15%</t>
-        </is>
-      </c>
-      <c r="E10" s="19" t="inlineStr">
-        <is>
-          <t>&lt; 10%</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="B11" s="8" t="inlineStr">
-        <is>
-          <t>Coste cubierto / Ticket</t>
-        </is>
-      </c>
-      <c r="C11" s="17" t="inlineStr">
-        <is>
-          <t>&lt; 60%</t>
-        </is>
-      </c>
-      <c r="D11" s="18" t="inlineStr">
-        <is>
-          <t>60% - 70%</t>
-        </is>
-      </c>
-      <c r="E11" s="19" t="inlineStr">
-        <is>
-          <t>&gt; 70%</t>
-        </is>
-      </c>
-    </row>
-    <row r="12"/>
-    <row r="13"/>
-    <row r="14">
-      <c r="A14" s="10" t="inlineStr">
-        <is>
-          <t>© 2026 AI Chef Pro · aichef.pro</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="B1:E1"/>
-    <mergeCell ref="A14:E14"/>
-  </mergeCells>
-  <pageMargins left="0.59" right="0.59" top="0.59" bottom="0.59" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
-  <headerFooter>
-    <oddHeader/>
-    <oddFooter>&amp;C&amp;8 AI Chef Pro · aichef.pro · Página &amp;P de &amp;N</oddFooter>
-    <evenHeader/>
-    <evenFooter/>
-    <firstHeader/>
-    <firstFooter/>
-  </headerFooter>
-</worksheet>
 </file>